--- a/META Model.xlsx
+++ b/META Model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerem\OneDrive\Masaüstü\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F05DD5-C41E-4FC8-981C-61170F58E239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E22B7D2-C955-406D-A800-A9B0393138E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6960" yWindow="528" windowWidth="26064" windowHeight="15744" xr2:uid="{64BEE0EA-45A1-4490-9445-11F5F6D37C44}"/>
+    <workbookView xWindow="28584" yWindow="0" windowWidth="26748" windowHeight="16680" xr2:uid="{64BEE0EA-45A1-4490-9445-11F5F6D37C44}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -530,6 +530,7 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -545,7 +546,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1127,7 +1127,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="438" row="6">
+  <wetp:taskpane dockstate="right" visibility="1" width="438" row="8">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -1255,11 +1255,11 @@
       <c r="G7" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I7" s="33">
+      <c r="I7" s="34">
         <v>78450</v>
       </c>
-      <c r="J7" s="33"/>
-      <c r="K7" s="33"/>
+      <c r="J7" s="34"/>
+      <c r="K7" s="34"/>
       <c r="M7" s="1" t="s">
         <v>46</v>
       </c>
@@ -1286,11 +1286,11 @@
       <c r="G8" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I8" s="37">
+      <c r="I8" s="38">
         <v>2004</v>
       </c>
-      <c r="J8" s="37"/>
-      <c r="K8" s="37"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
       <c r="M8" s="1" t="s">
         <v>47</v>
       </c>
@@ -1311,16 +1311,16 @@
         <v>2</v>
       </c>
       <c r="E9" s="19">
-        <v>713</v>
+        <v>650</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="I9" s="37" t="s">
+      <c r="I9" s="38" t="s">
         <v>77</v>
       </c>
-      <c r="J9" s="37"/>
-      <c r="K9" s="37"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
       <c r="M9" s="1" t="s">
         <v>52</v>
       </c>
@@ -1337,16 +1337,16 @@
       </c>
       <c r="E10" s="14">
         <f>E8/E9-1</f>
-        <v>0.19902001350677878</v>
+        <v>0.315232722508205</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="I10" s="37" t="s">
+      <c r="I10" s="38" t="s">
         <v>79</v>
       </c>
-      <c r="J10" s="37"/>
-      <c r="K10" s="37"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
       <c r="M10" s="1" t="s">
         <v>32</v>
       </c>
@@ -1368,16 +1368,16 @@
       </c>
       <c r="E11" s="14">
         <f>(K17/E9)^(1/2)-1</f>
-        <v>0.18636369610411307</v>
+        <v>0.24252728696630999</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="I11" s="37" t="s">
+      <c r="I11" s="38" t="s">
         <v>78</v>
       </c>
-      <c r="J11" s="37"/>
-      <c r="K11" s="37"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
       <c r="M11" s="1" t="s">
         <v>48</v>
       </c>
@@ -1387,11 +1387,11 @@
       <c r="R11" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="T11" s="35">
+      <c r="T11" s="36">
         <f>P17</f>
-        <v>1835262</v>
-      </c>
-      <c r="U11" s="35"/>
+        <v>1673100</v>
+      </c>
+      <c r="U11" s="36"/>
     </row>
     <row r="12" spans="2:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
@@ -1403,11 +1403,11 @@
       <c r="G12" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I12" s="34">
+      <c r="I12" s="35">
         <v>46022</v>
       </c>
-      <c r="J12" s="34"/>
-      <c r="K12" s="34"/>
+      <c r="J12" s="35"/>
+      <c r="K12" s="35"/>
       <c r="M12" s="1" t="s">
         <v>49</v>
       </c>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="P17" s="7">
         <f>E9*P11</f>
-        <v>1835262</v>
+        <v>1673100</v>
       </c>
       <c r="R17" s="1" t="s">
         <v>39</v>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P18" s="7">
         <f>P17+P10</f>
-        <v>1841874</v>
+        <v>1679712</v>
       </c>
       <c r="R18" s="1" t="s">
         <v>29</v>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="P19" s="25">
         <f>P17/60458</f>
-        <v>30.355982665652189</v>
+        <v>27.67375698832247</v>
       </c>
       <c r="R19" s="1" t="s">
         <v>40</v>
@@ -1609,31 +1609,31 @@
         <v>27</v>
       </c>
       <c r="E20" s="7">
-        <f>E17*E18</f>
+        <f t="shared" ref="E20:K20" si="0">E17*E18</f>
         <v>938540</v>
       </c>
       <c r="F20" s="7">
-        <f>F17*F18</f>
+        <f t="shared" si="0"/>
         <v>322800</v>
       </c>
       <c r="G20" s="7">
-        <f>G17*G18</f>
+        <f t="shared" si="0"/>
         <v>928390</v>
       </c>
       <c r="H20" s="7">
-        <f>H17*H18</f>
+        <f t="shared" si="0"/>
         <v>1547730</v>
       </c>
       <c r="I20" s="7">
-        <f>I17*I18</f>
+        <f t="shared" si="0"/>
         <v>1835262</v>
       </c>
       <c r="J20" s="7">
-        <f>J17*J18</f>
+        <f t="shared" si="0"/>
         <v>2309488.792089371</v>
       </c>
       <c r="K20" s="7">
-        <f>K17*K18</f>
+        <f t="shared" si="0"/>
         <v>2531652.8796830894</v>
       </c>
       <c r="M20" s="1" t="s">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="P20" s="25">
         <f>P17/76769</f>
-        <v>23.906290299469838</v>
+        <v>21.79395328843674</v>
       </c>
       <c r="R20" s="1" t="s">
         <v>41</v>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="P21" s="25">
         <f>P17/I36</f>
-        <v>9.1322014669148022</v>
+        <v>8.3252888548311663</v>
       </c>
       <c r="R21" s="1" t="s">
         <v>42</v>
@@ -1697,19 +1697,19 @@
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
-      <c r="E22" s="38">
+      <c r="E22" s="33">
         <v>14450</v>
       </c>
-      <c r="F22" s="38">
+      <c r="F22" s="33">
         <v>27280</v>
       </c>
-      <c r="G22" s="38">
+      <c r="G22" s="33">
         <v>37920</v>
       </c>
-      <c r="H22" s="38">
+      <c r="H22" s="33">
         <v>49770</v>
       </c>
-      <c r="I22" s="38">
+      <c r="I22" s="33">
         <v>83900</v>
       </c>
       <c r="J22" s="8">
@@ -1725,48 +1725,48 @@
       </c>
       <c r="P22" s="25">
         <f>P17/I51</f>
-        <v>22.038041716200151</v>
+        <v>20.090781368204908</v>
       </c>
       <c r="R22" s="5" t="s">
         <v>43</v>
       </c>
       <c r="S22" s="5"/>
-      <c r="T22" s="36">
+      <c r="T22" s="37">
         <f>U12+U19</f>
         <v>1</v>
       </c>
-      <c r="U22" s="36"/>
+      <c r="U22" s="37"/>
     </row>
     <row r="23" spans="2:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E23" s="7">
-        <f>E20+E22-E21</f>
+        <f t="shared" ref="E23:K23" si="1">E20+E22-E21</f>
         <v>904990</v>
       </c>
       <c r="F23" s="7">
-        <f>F20+F22-F21</f>
+        <f t="shared" si="1"/>
         <v>309340</v>
       </c>
       <c r="G23" s="7">
-        <f>G20+G22-G21</f>
+        <f t="shared" si="1"/>
         <v>900910</v>
       </c>
       <c r="H23" s="7">
-        <f>H20+H22-H21</f>
+        <f t="shared" si="1"/>
         <v>1526562</v>
       </c>
       <c r="I23" s="7">
-        <f>I20+I22-I21</f>
+        <f t="shared" si="1"/>
         <v>1836732</v>
       </c>
       <c r="J23" s="7">
-        <f>J20+J22-J21</f>
+        <f t="shared" si="1"/>
         <v>2306999.8711704938</v>
       </c>
       <c r="K23" s="7">
-        <f>K20+K22-K21</f>
+        <f t="shared" si="1"/>
         <v>2508882.6743786265</v>
       </c>
       <c r="R23" s="1" t="s">
@@ -1891,35 +1891,35 @@
         <v>1.7513736263736264E-2</v>
       </c>
       <c r="G28" s="10">
-        <f t="shared" ref="G28:K28" si="0">(G27-F27)/F27</f>
+        <f t="shared" ref="G28:K28" si="2">(G27-F27)/F27</f>
         <v>3.442456969287884E-2</v>
       </c>
       <c r="H28" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2.4143556280587276E-2</v>
       </c>
       <c r="I28" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2.6799999999999984E-2</v>
       </c>
       <c r="J28" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2.2999999999999875E-2</v>
       </c>
       <c r="K28" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.8999999999999923E-2</v>
       </c>
       <c r="L28" s="10">
-        <f t="shared" ref="L28" si="1">(L27-K27)/K27</f>
+        <f t="shared" ref="L28" si="3">(L27-K27)/K27</f>
         <v>1.8000000000000009E-2</v>
       </c>
       <c r="M28" s="10">
-        <f t="shared" ref="M28" si="2">(M27-L27)/L27</f>
+        <f t="shared" ref="M28" si="4">(M27-L27)/L27</f>
         <v>1.5999999999999948E-2</v>
       </c>
       <c r="N28" s="10">
-        <f t="shared" ref="N28" si="3">(N27-M27)/M27</f>
+        <f t="shared" ref="N28" si="5">(N27-M27)/M27</f>
         <v>1.3999999999999995E-2</v>
       </c>
       <c r="T28"/>
@@ -1998,7 +1998,7 @@
         <v>2.9999999999999971E-2</v>
       </c>
       <c r="K31" s="10">
-        <f t="shared" ref="K31" si="4">(K30-J30)/J30</f>
+        <f t="shared" ref="K31" si="6">(K30-J30)/J30</f>
         <v>1.9999999999999983E-2</v>
       </c>
       <c r="L31" s="10"/>
@@ -2023,23 +2023,23 @@
         <v>76</v>
       </c>
       <c r="E33" s="7">
-        <f t="shared" ref="E33:I33" si="5">E36/E27</f>
+        <f t="shared" ref="E33:I33" si="7">E36/E27</f>
         <v>40.497596153846153</v>
       </c>
       <c r="F33" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>39.355045561930474</v>
       </c>
       <c r="G33" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>44.0137030995106</v>
       </c>
       <c r="H33" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>52.405543166613569</v>
       </c>
       <c r="I33" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>62.351285640408882</v>
       </c>
       <c r="J33" s="7">
@@ -2093,19 +2093,19 @@
         <v>0.17479534299334212</v>
       </c>
       <c r="K34" s="10">
-        <f t="shared" ref="K34:N34" si="6">(K33-J33)/J33</f>
+        <f t="shared" ref="K34:N34" si="8">(K33-J33)/J33</f>
         <v>0.14999999999999997</v>
       </c>
       <c r="L34" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0.13999999999999985</v>
       </c>
       <c r="M34" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0.12500000000000003</v>
       </c>
       <c r="N34" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0.10500000000000004</v>
       </c>
       <c r="T34"/>
@@ -2142,23 +2142,23 @@
         <v>200966</v>
       </c>
       <c r="J36" s="7">
-        <f t="shared" ref="J36:N36" si="7">J27*J33</f>
+        <f t="shared" ref="J36:N36" si="9">J27*J33</f>
         <v>241524.08108069998</v>
       </c>
       <c r="K36" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>283029.99441441824</v>
       </c>
       <c r="L36" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>328461.96911782061</v>
       </c>
       <c r="M36" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>375432.03070166893</v>
       </c>
       <c r="N36" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>420660.32744029898</v>
       </c>
     </row>
@@ -2193,19 +2193,19 @@
         <v>0.20181563588218893</v>
       </c>
       <c r="K37" s="10">
-        <f t="shared" ref="K37" si="8">(K36-J36)/J36</f>
+        <f t="shared" ref="K37" si="10">(K36-J36)/J36</f>
         <v>0.17184999999999986</v>
       </c>
       <c r="L37" s="10">
-        <f t="shared" ref="L37" si="9">(L36-K36)/K36</f>
+        <f t="shared" ref="L37" si="11">(L36-K36)/K36</f>
         <v>0.16051999999999986</v>
       </c>
       <c r="M37" s="10">
-        <f t="shared" ref="M37" si="10">(M36-L36)/L36</f>
+        <f t="shared" ref="M37" si="12">(M36-L36)/L36</f>
         <v>0.1429999999999999</v>
       </c>
       <c r="N37" s="10">
-        <f t="shared" ref="N37" si="11">(N36-M36)/M36</f>
+        <f t="shared" ref="N37" si="13">(N36-M36)/M36</f>
         <v>0.12046999999999997</v>
       </c>
       <c r="T37"/>
@@ -2275,39 +2275,39 @@
         <v>0.19205623722748433</v>
       </c>
       <c r="F40" s="10">
-        <f t="shared" ref="F40:N40" si="12">F39/F36</f>
+        <f t="shared" ref="F40:N40" si="14">F39/F36</f>
         <v>0.21652702621581524</v>
       </c>
       <c r="G40" s="10">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.1924211649938474</v>
       </c>
       <c r="H40" s="10">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.18335450848323109</v>
       </c>
       <c r="I40" s="10">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.18000059711593006</v>
       </c>
       <c r="J40" s="10">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.19800000000000001</v>
       </c>
       <c r="K40" s="10">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.21</v>
       </c>
       <c r="L40" s="10">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.22500000000000003</v>
       </c>
       <c r="M40" s="10">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.24399999999999997</v>
       </c>
       <c r="N40" s="10">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0.25</v>
       </c>
     </row>
@@ -2320,39 +2320,39 @@
         <v>95280</v>
       </c>
       <c r="F42" s="7">
-        <f t="shared" ref="F42:N42" si="13">F36-F39</f>
+        <f t="shared" ref="F42:N42" si="15">F36-F39</f>
         <v>91360</v>
       </c>
       <c r="G42" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>108944</v>
       </c>
       <c r="H42" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>134339</v>
       </c>
       <c r="I42" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>164792</v>
       </c>
       <c r="J42" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>193702.31302672139</v>
       </c>
       <c r="K42" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>223593.69558739039</v>
       </c>
       <c r="L42" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>254558.02606631097</v>
       </c>
       <c r="M42" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>283826.61521046172</v>
       </c>
       <c r="N42" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>315495.2455802242</v>
       </c>
     </row>
@@ -2365,39 +2365,39 @@
         <v>0.80794376277251567</v>
       </c>
       <c r="F43" s="10">
-        <f t="shared" ref="F43:N43" si="14">F42/F36</f>
+        <f t="shared" ref="F43:N43" si="16">F42/F36</f>
         <v>0.78347297378418479</v>
       </c>
       <c r="G43" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.80757883500615257</v>
       </c>
       <c r="H43" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.81664549151676891</v>
       </c>
       <c r="I43" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.81999940288406992</v>
       </c>
       <c r="J43" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.80200000000000005</v>
       </c>
       <c r="K43" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.78999999999999992</v>
       </c>
       <c r="L43" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.77500000000000002</v>
       </c>
       <c r="M43" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.75600000000000001</v>
       </c>
       <c r="N43" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.74999999999999989</v>
       </c>
     </row>
@@ -2451,39 +2451,39 @@
         <v>0.30068515801880791</v>
       </c>
       <c r="F46" s="10">
-        <f t="shared" ref="F46:N46" si="15">F45/F36</f>
+        <f t="shared" ref="F46:N46" si="17">F45/F36</f>
         <v>0.2322119218928213</v>
       </c>
       <c r="G46" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.17574980356110362</v>
       </c>
       <c r="H46" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.12818159160126685</v>
       </c>
       <c r="I46" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.12013474916154972</v>
       </c>
       <c r="J46" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.14000000000000001</v>
       </c>
       <c r="K46" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.13</v>
       </c>
       <c r="L46" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.12000000000000001</v>
       </c>
       <c r="M46" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.115</v>
       </c>
       <c r="N46" s="10">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.11</v>
       </c>
     </row>
@@ -2537,39 +2537,39 @@
         <v>0.20906647219937419</v>
       </c>
       <c r="F49" s="10">
-        <f t="shared" ref="F49:N49" si="16">F48/F36</f>
+        <f t="shared" ref="F49:N49" si="18">F48/F36</f>
         <v>0.30304693462768739</v>
       </c>
       <c r="G49" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.28526634149234259</v>
       </c>
       <c r="H49" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.26669746688469981</v>
       </c>
       <c r="I49" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.28548112616064408</v>
       </c>
       <c r="J49" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.30099999999999999</v>
       </c>
       <c r="K49" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.30199999999999999</v>
       </c>
       <c r="L49" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.315</v>
       </c>
       <c r="M49" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.3</v>
       </c>
       <c r="N49" s="10">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0.3</v>
       </c>
     </row>
@@ -2620,39 +2620,39 @@
         <v>0.39645040660058173</v>
       </c>
       <c r="F52" s="10">
-        <f t="shared" ref="F52:N52" si="17">F51/F36</f>
+        <f t="shared" ref="F52:N52" si="19">F51/F36</f>
         <v>0.24822269293107735</v>
       </c>
       <c r="G52" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.34655527716416362</v>
       </c>
       <c r="H52" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.42176643303080225</v>
       </c>
       <c r="I52" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.41438352756187613</v>
       </c>
       <c r="J52" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.35766702687975976</v>
       </c>
       <c r="K52" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.34645444629597438</v>
       </c>
       <c r="L52" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.32798317652829034</v>
       </c>
       <c r="M52" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.33847671378092437</v>
       </c>
       <c r="N52" s="10">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0.37</v>
       </c>
     </row>
@@ -2705,39 +2705,39 @@
         <v>0.1692511710478472</v>
       </c>
       <c r="F55" s="10">
-        <f t="shared" ref="F55:N55" si="18">F54/F51</f>
+        <f t="shared" ref="F55:N55" si="20">F54/F51</f>
         <v>0.19416134047331146</v>
       </c>
       <c r="G55" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.17819939680434643</v>
       </c>
       <c r="H55" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.11968694599386</v>
       </c>
       <c r="I55" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.30986947176291174</v>
       </c>
       <c r="J55" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.14000000000000001</v>
       </c>
       <c r="K55" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.14499999999999999</v>
       </c>
       <c r="L55" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.15</v>
       </c>
       <c r="M55" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.17</v>
       </c>
       <c r="N55" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0.17499999999999999</v>
       </c>
     </row>
@@ -2848,39 +2848,39 @@
         <v>0.42904077126083912</v>
       </c>
       <c r="F60" s="10">
-        <f t="shared" ref="F60:M60" si="19">F59/F63</f>
+        <f t="shared" ref="F60:M60" si="21">F59/F63</f>
         <v>0.27635137284846173</v>
       </c>
       <c r="G60" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0.4099244480305142</v>
       </c>
       <c r="H60" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0.41598668670818123</v>
       </c>
       <c r="I60" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0.2578134736550578</v>
       </c>
       <c r="J60" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0.23699999999999999</v>
       </c>
       <c r="K60" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0.315</v>
       </c>
       <c r="L60" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0.36</v>
       </c>
       <c r="M60" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0.41</v>
       </c>
       <c r="N60" s="10">
-        <f t="shared" ref="N60" si="20">N59/N63</f>
+        <f t="shared" ref="N60" si="22">N59/N63</f>
         <v>0.47999999999999993</v>
       </c>
     </row>
@@ -2893,39 +2893,39 @@
         <v>6.7549118537425054E-2</v>
       </c>
       <c r="F61" s="10">
-        <f t="shared" ref="F61:N61" si="21">F59/F36</f>
+        <f t="shared" ref="F61:N61" si="23">F59/F36</f>
         <v>7.44882470478265E-2</v>
       </c>
       <c r="G61" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>8.2852737542808849E-2</v>
       </c>
       <c r="H61" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>9.4212193238946876E-2</v>
       </c>
       <c r="I61" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>9.2642536548470891E-2</v>
       </c>
       <c r="J61" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0.12265857660007598</v>
       </c>
       <c r="K61" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0.15303148378182477</v>
       </c>
       <c r="L61" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0.16125154501829478</v>
       </c>
       <c r="M61" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0.17031185346784997</v>
       </c>
       <c r="N61" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0.17439261849671672</v>
       </c>
     </row>
@@ -3036,39 +3036,39 @@
         <v>5.9357749154152076E-3</v>
       </c>
       <c r="F67" s="10">
-        <f t="shared" ref="F67:N67" si="22">F66/F36</f>
+        <f t="shared" ref="F67:N67" si="24">F66/F36</f>
         <v>4.8709790839472085E-2</v>
       </c>
       <c r="G67" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>2.8465108004329068E-2</v>
       </c>
       <c r="H67" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>6.3829399213378643E-3</v>
       </c>
       <c r="I67" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-4.4286098145955039E-3</v>
       </c>
       <c r="J67" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-1.8424663826846857E-3</v>
       </c>
       <c r="K67" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-5.1884960215552015E-4</v>
       </c>
       <c r="L67" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>4.4708372294792009E-4</v>
       </c>
       <c r="M67" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>9.3875847338145961E-4</v>
       </c>
       <c r="N67" s="10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>1.0472820260487336E-3</v>
       </c>
     </row>
@@ -3137,39 +3137,39 @@
         <v>117929</v>
       </c>
       <c r="F71" s="7">
-        <f t="shared" ref="F71:N71" si="23">F36</f>
+        <f t="shared" ref="F71:N71" si="25">F36</f>
         <v>116609</v>
       </c>
       <c r="G71" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>134902</v>
       </c>
       <c r="H71" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>164501</v>
       </c>
       <c r="I71" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>200966</v>
       </c>
       <c r="J71" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>241524.08108069998</v>
       </c>
       <c r="K71" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>283029.99441441824</v>
       </c>
       <c r="L71" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>328461.96911782061</v>
       </c>
       <c r="M71" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>375432.03070166893</v>
       </c>
       <c r="N71" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>420660.32744029898</v>
       </c>
     </row>
@@ -3184,39 +3184,39 @@
         <v>0.37182574303495608</v>
       </c>
       <c r="F72" s="10">
-        <f t="shared" ref="F72:N72" si="24">F37</f>
+        <f t="shared" ref="F72:N72" si="26">F37</f>
         <v>-1.1193175554782962E-2</v>
       </c>
       <c r="G72" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0.15687468377226457</v>
       </c>
       <c r="H72" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0.21941112807816043</v>
       </c>
       <c r="I72" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0.22167038498246211</v>
       </c>
       <c r="J72" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0.20181563588218893</v>
       </c>
       <c r="K72" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0.17184999999999986</v>
       </c>
       <c r="L72" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0.16051999999999986</v>
       </c>
       <c r="M72" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0.1429999999999999</v>
       </c>
       <c r="N72" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0.12046999999999997</v>
       </c>
     </row>
@@ -3279,39 +3279,39 @@
         <v>0.39645040660058173</v>
       </c>
       <c r="F75" s="10">
-        <f t="shared" ref="F75:N75" si="25">F74/F71</f>
+        <f t="shared" ref="F75:N75" si="27">F74/F71</f>
         <v>0.24822269293107735</v>
       </c>
       <c r="G75" s="10">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.34655527716416362</v>
       </c>
       <c r="H75" s="10">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.42176643303080225</v>
       </c>
       <c r="I75" s="10">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.41438352756187613</v>
       </c>
       <c r="J75" s="10">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.35766702687975976</v>
       </c>
       <c r="K75" s="10">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.34645444629597438</v>
       </c>
       <c r="L75" s="10">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.32798317652829034</v>
       </c>
       <c r="M75" s="10">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.33847671378092437</v>
       </c>
       <c r="N75" s="10">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.37</v>
       </c>
     </row>
@@ -3327,39 +3327,39 @@
         <v>13</v>
       </c>
       <c r="E77" s="7">
-        <f t="shared" ref="E77:N77" si="26">E54</f>
+        <f t="shared" ref="E77:M77" si="28">E54</f>
         <v>7913</v>
       </c>
       <c r="F77" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>5620</v>
       </c>
       <c r="G77" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>8331</v>
       </c>
       <c r="H77" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>8304</v>
       </c>
       <c r="I77" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>25805</v>
       </c>
       <c r="J77" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>12093.928</v>
       </c>
       <c r="K77" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>14218.264999999999</v>
       </c>
       <c r="L77" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>16159.5</v>
       </c>
       <c r="M77" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>21602.75</v>
       </c>
       <c r="N77" s="7">
@@ -3378,39 +3378,39 @@
         <v>0.1692511710478472</v>
       </c>
       <c r="F78" s="10">
-        <f t="shared" ref="F78:N78" si="27">F55</f>
+        <f t="shared" ref="F78:N78" si="29">F55</f>
         <v>0.19416134047331146</v>
       </c>
       <c r="G78" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0.17819939680434643</v>
       </c>
       <c r="H78" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0.11968694599386</v>
       </c>
       <c r="I78" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0.30986947176291174</v>
       </c>
       <c r="J78" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0.14000000000000001</v>
       </c>
       <c r="K78" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0.14499999999999999</v>
       </c>
       <c r="L78" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0.15</v>
       </c>
       <c r="M78" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0.17</v>
       </c>
       <c r="N78" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>0.17499999999999999</v>
       </c>
     </row>
@@ -3425,39 +3425,39 @@
         <v>38840</v>
       </c>
       <c r="F80" s="29">
-        <f t="shared" ref="F80:N80" si="28">F74-F77</f>
+        <f t="shared" ref="F80:N80" si="30">F74-F77</f>
         <v>23325</v>
       </c>
       <c r="G80" s="29">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>38420</v>
       </c>
       <c r="H80" s="29">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>61077</v>
       </c>
       <c r="I80" s="29">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>57472</v>
       </c>
       <c r="J80" s="29">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>74291.271999999997</v>
       </c>
       <c r="K80" s="29">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>83838.735000000001</v>
       </c>
       <c r="L80" s="29">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>91570.5</v>
       </c>
       <c r="M80" s="29">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>105472.25</v>
       </c>
       <c r="N80" s="30">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>128406.56495115126</v>
       </c>
     </row>
@@ -3470,39 +3470,39 @@
         <v>7966</v>
       </c>
       <c r="F82" s="7">
-        <f t="shared" ref="F82:N82" si="29">F59</f>
+        <f t="shared" ref="F82:N82" si="31">F59</f>
         <v>8686</v>
       </c>
       <c r="G82" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>11177</v>
       </c>
       <c r="H82" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>15498</v>
       </c>
       <c r="I82" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>18618</v>
       </c>
       <c r="J82" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>29625</v>
       </c>
       <c r="K82" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>43312.5</v>
       </c>
       <c r="L82" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>52965</v>
       </c>
       <c r="M82" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>63940.524999999994</v>
       </c>
       <c r="N82" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>73360.055999999997</v>
       </c>
       <c r="P82" s="7"/>
@@ -3518,39 +3518,39 @@
         <v>6.7549118537425054E-2</v>
       </c>
       <c r="F83" s="10">
-        <f t="shared" ref="F83:N83" si="30">F82/F71</f>
+        <f t="shared" ref="F83:N83" si="32">F82/F71</f>
         <v>7.44882470478265E-2</v>
       </c>
       <c r="G83" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>8.2852737542808849E-2</v>
       </c>
       <c r="H83" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>9.4212193238946876E-2</v>
       </c>
       <c r="I83" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>9.2642536548470891E-2</v>
       </c>
       <c r="J83" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0.12265857660007598</v>
       </c>
       <c r="K83" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0.15303148378182477</v>
       </c>
       <c r="L83" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0.16125154501829478</v>
       </c>
       <c r="M83" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0.17031185346784997</v>
       </c>
       <c r="N83" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0.17439261849671672</v>
       </c>
     </row>
@@ -3563,39 +3563,39 @@
         <v>18567</v>
       </c>
       <c r="F85" s="7">
-        <f t="shared" ref="F85:N85" si="31">F63</f>
+        <f t="shared" ref="F85:N85" si="33">F63</f>
         <v>31431</v>
       </c>
       <c r="G85" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>27266</v>
       </c>
       <c r="H85" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>37256</v>
       </c>
       <c r="I85" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>72215</v>
       </c>
       <c r="J85" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>125000</v>
       </c>
       <c r="K85" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>137500</v>
       </c>
       <c r="L85" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>147125</v>
       </c>
       <c r="M85" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>155952.5</v>
       </c>
       <c r="N85" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>152833.45000000001</v>
       </c>
       <c r="Q85" s="7"/>
@@ -3611,39 +3611,39 @@
         <v>0.15744218979216307</v>
       </c>
       <c r="F86" s="10">
-        <f t="shared" ref="F86:N86" si="32">F85/F71</f>
+        <f t="shared" ref="F86:N86" si="34">F85/F71</f>
         <v>0.26954180209074774</v>
       </c>
       <c r="G86" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.20211709240782197</v>
       </c>
       <c r="H86" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.22647886638986997</v>
       </c>
       <c r="I86" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.35933939074271271</v>
       </c>
       <c r="J86" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.51754673670918139</v>
       </c>
       <c r="K86" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.48581423422801517</v>
       </c>
       <c r="L86" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.44792095838415219</v>
       </c>
       <c r="M86" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.41539476455573171</v>
       </c>
       <c r="N86" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.36331795520149324</v>
       </c>
     </row>
@@ -3703,39 +3703,39 @@
         <v>5.9357749154152076E-3</v>
       </c>
       <c r="F89" s="10">
-        <f t="shared" ref="F89:N89" si="33">F88/F71</f>
+        <f t="shared" ref="F89:N89" si="35">F88/F71</f>
         <v>4.8709790839472085E-2</v>
       </c>
       <c r="G89" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>2.8465108004329068E-2</v>
       </c>
       <c r="H89" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>6.3829399213378643E-3</v>
       </c>
       <c r="I89" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>-1.5176696555636277E-2</v>
       </c>
       <c r="J89" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>-6.3140701878520123E-3</v>
       </c>
       <c r="K89" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>-1.7780800972745355E-3</v>
       </c>
       <c r="L89" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>1.53214084830467E-3</v>
       </c>
       <c r="M89" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>3.2170936447342155E-3</v>
       </c>
       <c r="N89" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>3.5890002016276826E-3</v>
       </c>
     </row>
@@ -3786,11 +3786,11 @@
         <v>34488.506757371164</v>
       </c>
       <c r="M91" s="12">
-        <f t="shared" ref="M91:N91" si="34">M71*0.105</f>
+        <f t="shared" ref="M91:N91" si="36">M71*0.105</f>
         <v>39420.363223675238</v>
       </c>
       <c r="N91" s="12">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>44169.334381231391</v>
       </c>
     </row>
@@ -3805,39 +3805,39 @@
         <v>7.7673854607433285E-2</v>
       </c>
       <c r="F92" s="10">
-        <f t="shared" ref="F92:J92" si="35">F91/F71</f>
+        <f t="shared" ref="F92:J92" si="37">F91/F71</f>
         <v>0.10283940347657557</v>
       </c>
       <c r="G92" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0.10400142325540021</v>
       </c>
       <c r="H92" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>9.2035914675290723E-2</v>
       </c>
       <c r="I92" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>9.9519321676303452E-2</v>
       </c>
       <c r="J92" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>0.11</v>
       </c>
       <c r="K92" s="10">
-        <f t="shared" ref="K92" si="36">K91/K71</f>
+        <f t="shared" ref="K92" si="38">K91/K71</f>
         <v>0.11</v>
       </c>
       <c r="L92" s="10">
-        <f t="shared" ref="L92" si="37">L91/L71</f>
+        <f t="shared" ref="L92" si="39">L91/L71</f>
         <v>0.105</v>
       </c>
       <c r="M92" s="10">
-        <f t="shared" ref="M92" si="38">M91/M71</f>
+        <f t="shared" ref="M92" si="40">M91/M71</f>
         <v>0.105</v>
       </c>
       <c r="N92" s="10">
-        <f t="shared" ref="N92" si="39">N91/N71</f>
+        <f t="shared" ref="N92" si="41">N91/N71</f>
         <v>0.105</v>
       </c>
     </row>
@@ -3864,23 +3864,23 @@
         <v>20825</v>
       </c>
       <c r="J94" s="7">
-        <f t="shared" ref="J94:N94" si="40">J80+J82-J85+J88+J91</f>
+        <f t="shared" ref="J94:N94" si="42">J80+J82-J85+J88+J91</f>
         <v>3958.9209188769964</v>
       </c>
       <c r="K94" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>20281.284385586008</v>
       </c>
       <c r="L94" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>32402.256757371164</v>
       </c>
       <c r="M94" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>54088.438223675228</v>
       </c>
       <c r="N94" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>94612.255332382629</v>
       </c>
       <c r="O94" s="7"/>
@@ -3905,39 +3905,39 @@
         <v>0.33169110227340182</v>
       </c>
       <c r="F95" s="10">
-        <f t="shared" ref="F95:N95" si="41">F94/F71</f>
+        <f t="shared" ref="F95:N95" si="43">F94/F71</f>
         <v>0.15812673121285664</v>
       </c>
       <c r="G95" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0.31882403522557118</v>
       </c>
       <c r="H95" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0.31673363687758738</v>
       </c>
       <c r="I95" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0.10362449369545097</v>
       </c>
       <c r="J95" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>1.6391412819636027E-2</v>
       </c>
       <c r="K95" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>7.1657721039593211E-2</v>
       </c>
       <c r="L95" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>9.8648427531494054E-2</v>
       </c>
       <c r="M95" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0.1440698549950197</v>
       </c>
       <c r="N95" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>0.22491366349685116</v>
       </c>
     </row>

--- a/META Model.xlsx
+++ b/META Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerem\OneDrive\Masaüstü\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E22B7D2-C955-406D-A800-A9B0393138E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A02D53C4-B977-4F18-8B1E-4D8C901C82EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28584" yWindow="0" windowWidth="26748" windowHeight="16680" xr2:uid="{64BEE0EA-45A1-4490-9445-11F5F6D37C44}"/>
+    <workbookView xWindow="13704" yWindow="0" windowWidth="33252" windowHeight="16344" xr2:uid="{64BEE0EA-45A1-4490-9445-11F5F6D37C44}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -381,11 +381,13 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="calibri"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1265,7 +1267,7 @@
       </c>
       <c r="P7" s="7">
         <f>SUM(J97:N97)</f>
-        <v>148959.44055637275</v>
+        <v>164233.26687311727</v>
       </c>
       <c r="R7" s="1" t="s">
         <v>34</v>
@@ -1281,7 +1283,7 @@
       </c>
       <c r="E8" s="19">
         <f>P12/P11</f>
-        <v>854.90126963033322</v>
+        <v>818.5724174061304</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>57</v>
@@ -1296,7 +1298,7 @@
       </c>
       <c r="P8" s="7">
         <f>N51*U8</f>
-        <v>3112886.4230582123</v>
+        <v>2948355.1141003342</v>
       </c>
       <c r="R8" s="1" t="s">
         <v>51</v>
@@ -1311,7 +1313,7 @@
         <v>2</v>
       </c>
       <c r="E9" s="19">
-        <v>650</v>
+        <v>580</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>58</v>
@@ -1326,7 +1328,7 @@
       </c>
       <c r="P9" s="7">
         <f>P8/(1+U7)^4.5</f>
-        <v>2058168.427472105</v>
+        <v>1949384.1355302625</v>
       </c>
       <c r="R9" s="32"/>
       <c r="U9" s="7"/>
@@ -1337,7 +1339,7 @@
       </c>
       <c r="E10" s="14">
         <f>E8/E9-1</f>
-        <v>0.315232722508205</v>
+        <v>0.41133175414850065</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>59</v>
@@ -1368,7 +1370,7 @@
       </c>
       <c r="E11" s="14">
         <f>(K17/E9)^(1/2)-1</f>
-        <v>0.24252728696630999</v>
+        <v>0.28708773583480296</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>60</v>
@@ -1389,7 +1391,7 @@
       </c>
       <c r="T11" s="36">
         <f>P17</f>
-        <v>1673100</v>
+        <v>1492920</v>
       </c>
       <c r="U11" s="36"/>
     </row>
@@ -1398,7 +1400,7 @@
         <v>66</v>
       </c>
       <c r="E12" s="17">
-        <v>46051</v>
+        <v>46107</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>61</v>
@@ -1413,7 +1415,7 @@
       </c>
       <c r="P12" s="7">
         <f>P9+P7-P10</f>
-        <v>2200515.8680284778</v>
+        <v>2107005.4024033798</v>
       </c>
       <c r="R12" s="1" t="s">
         <v>35</v>
@@ -1504,7 +1506,7 @@
       <c r="O16" s="1"/>
       <c r="P16" s="7">
         <f>SUM(J97:N97)</f>
-        <v>148959.44055637275</v>
+        <v>164233.26687311727</v>
       </c>
     </row>
     <row r="17" spans="2:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1528,18 +1530,18 @@
       </c>
       <c r="J17" s="6">
         <f>((SUM(K97:N97)+P9)*(1+$U$7)^0.5+J21-J22)/J18</f>
-        <v>906.30029592324615</v>
+        <v>867.8781878353816</v>
       </c>
       <c r="K17" s="6">
         <f>((SUM(L97:N97)+P9)*(1+$U$7)^1.5+K21-K22)/K18</f>
-        <v>1003.5181382563081</v>
+        <v>960.82500704708866</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>27</v>
       </c>
       <c r="P17" s="7">
         <f>E9*P11</f>
-        <v>1673100</v>
+        <v>1492920</v>
       </c>
       <c r="R17" s="1" t="s">
         <v>39</v>
@@ -1580,7 +1582,7 @@
       </c>
       <c r="P18" s="7">
         <f>P17+P10</f>
-        <v>1679712</v>
+        <v>1499532</v>
       </c>
       <c r="R18" s="1" t="s">
         <v>29</v>
@@ -1595,7 +1597,7 @@
       </c>
       <c r="P19" s="25">
         <f>P17/60458</f>
-        <v>27.67375698832247</v>
+        <v>24.693506235733899</v>
       </c>
       <c r="R19" s="1" t="s">
         <v>40</v>
@@ -1630,18 +1632,18 @@
       </c>
       <c r="J20" s="7">
         <f t="shared" si="0"/>
-        <v>2309488.792089371</v>
+        <v>2211579.2709333892</v>
       </c>
       <c r="K20" s="7">
         <f t="shared" si="0"/>
-        <v>2531652.8796830894</v>
+        <v>2423947.6131332358</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>71</v>
       </c>
       <c r="P20" s="25">
         <f>P17/76769</f>
-        <v>21.79395328843674</v>
+        <v>19.446912165066628</v>
       </c>
       <c r="R20" s="1" t="s">
         <v>41</v>
@@ -1671,18 +1673,18 @@
       </c>
       <c r="J21" s="11">
         <f>I21+J94</f>
-        <v>86388.920918877004</v>
+        <v>90200.535732490505</v>
       </c>
       <c r="K21" s="11">
         <f>J21+K94</f>
-        <v>106670.20530446302</v>
+        <v>116893.12024962489</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>69</v>
       </c>
       <c r="P21" s="25">
         <f>P17/I36</f>
-        <v>8.3252888548311663</v>
+        <v>7.4287192858493478</v>
       </c>
       <c r="R21" s="1" t="s">
         <v>42</v>
@@ -1725,7 +1727,7 @@
       </c>
       <c r="P22" s="25">
         <f>P17/I51</f>
-        <v>20.090781368204908</v>
+        <v>17.927158759321301</v>
       </c>
       <c r="R22" s="5" t="s">
         <v>43</v>
@@ -1763,18 +1765,17 @@
       </c>
       <c r="J23" s="7">
         <f t="shared" si="1"/>
-        <v>2306999.8711704938</v>
+        <v>2205278.7352008987</v>
       </c>
       <c r="K23" s="7">
         <f t="shared" si="1"/>
-        <v>2508882.6743786265</v>
+        <v>2390954.492883611</v>
       </c>
       <c r="R23" s="1" t="s">
         <v>34</v>
       </c>
       <c r="U23" s="9">
-        <f>U22</f>
-        <v>0</v>
+        <v>9.6299999999999997E-2</v>
       </c>
     </row>
     <row r="25" spans="2:21" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2043,23 +2044,23 @@
         <v>62.351285640408882</v>
       </c>
       <c r="J33" s="7">
-        <v>73.25</v>
+        <v>75.5</v>
       </c>
       <c r="K33" s="7">
         <f>J33*1.15</f>
-        <v>84.237499999999997</v>
+        <v>86.824999999999989</v>
       </c>
       <c r="L33" s="7">
         <f>K33*1.14</f>
-        <v>96.030749999999983</v>
+        <v>98.980499999999978</v>
       </c>
       <c r="M33" s="7">
         <f>L33*1.125</f>
-        <v>108.03459374999998</v>
+        <v>111.35306249999998</v>
       </c>
       <c r="N33" s="7">
         <f>M33*(1+M34-0.02)</f>
-        <v>119.37822609374999</v>
+        <v>123.04513406249997</v>
       </c>
     </row>
     <row r="34" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2090,15 +2091,15 @@
       </c>
       <c r="J34" s="10">
         <f>(J33-I33)/I33</f>
-        <v>0.17479534299334212</v>
+        <v>0.2108812067712946</v>
       </c>
       <c r="K34" s="10">
         <f t="shared" ref="K34:N34" si="8">(K33-J33)/J33</f>
-        <v>0.14999999999999997</v>
+        <v>0.14999999999999986</v>
       </c>
       <c r="L34" s="10">
         <f t="shared" si="8"/>
-        <v>0.13999999999999985</v>
+        <v>0.1399999999999999</v>
       </c>
       <c r="M34" s="10">
         <f t="shared" si="8"/>
@@ -2106,7 +2107,7 @@
       </c>
       <c r="N34" s="10">
         <f t="shared" si="8"/>
-        <v>0.10500000000000004</v>
+        <v>0.10499999999999993</v>
       </c>
       <c r="T34"/>
     </row>
@@ -2143,23 +2144,23 @@
       </c>
       <c r="J36" s="7">
         <f t="shared" ref="J36:N36" si="9">J27*J33</f>
-        <v>241524.08108069998</v>
+        <v>248942.90950979997</v>
       </c>
       <c r="K36" s="7">
         <f t="shared" si="9"/>
-        <v>283029.99441441824</v>
+        <v>291723.74850905902</v>
       </c>
       <c r="L36" s="7">
         <f t="shared" si="9"/>
-        <v>328461.96911782061</v>
+        <v>338551.24461973313</v>
       </c>
       <c r="M36" s="7">
         <f t="shared" si="9"/>
-        <v>375432.03070166893</v>
+        <v>386964.07260035496</v>
       </c>
       <c r="N36" s="7">
         <f t="shared" si="9"/>
-        <v>420660.32744029898</v>
+        <v>433581.63442651974</v>
       </c>
     </row>
     <row r="37" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2190,11 +2191,11 @@
       </c>
       <c r="J37" s="10">
         <f>(J36-I36)/I36</f>
-        <v>0.20181563588218893</v>
+        <v>0.23873147452703425</v>
       </c>
       <c r="K37" s="10">
         <f t="shared" ref="K37" si="10">(K36-J36)/J36</f>
-        <v>0.17184999999999986</v>
+        <v>0.17184999999999973</v>
       </c>
       <c r="L37" s="10">
         <f t="shared" ref="L37" si="11">(L36-K36)/K36</f>
@@ -2202,11 +2203,11 @@
       </c>
       <c r="M37" s="10">
         <f t="shared" ref="M37" si="12">(M36-L36)/L36</f>
-        <v>0.1429999999999999</v>
+        <v>0.14299999999999999</v>
       </c>
       <c r="N37" s="10">
         <f t="shared" ref="N37" si="13">(N36-M36)/M36</f>
-        <v>0.12046999999999997</v>
+        <v>0.12047000000000004</v>
       </c>
       <c r="T37"/>
     </row>
@@ -2247,23 +2248,23 @@
       </c>
       <c r="J39" s="7">
         <f>J36*0.198</f>
-        <v>47821.768053978602</v>
+        <v>49290.696082940398</v>
       </c>
       <c r="K39" s="7">
         <f>K36*0.21</f>
-        <v>59436.298827027829</v>
+        <v>61261.987186902392</v>
       </c>
       <c r="L39" s="7">
         <f>L36*0.225</f>
-        <v>73903.943051509646</v>
+        <v>76174.030039439953</v>
       </c>
       <c r="M39" s="7">
         <f>M36*0.244</f>
-        <v>91605.415491207212</v>
+        <v>94419.233714486603</v>
       </c>
       <c r="N39" s="7">
         <f>N36*0.25</f>
-        <v>105165.08186007474</v>
+        <v>108395.40860662994</v>
       </c>
     </row>
     <row r="40" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2300,7 +2301,7 @@
       </c>
       <c r="L40" s="10">
         <f t="shared" si="14"/>
-        <v>0.22500000000000003</v>
+        <v>0.22500000000000001</v>
       </c>
       <c r="M40" s="10">
         <f t="shared" si="14"/>
@@ -2337,23 +2338,23 @@
       </c>
       <c r="J42" s="7">
         <f t="shared" si="15"/>
-        <v>193702.31302672139</v>
+        <v>199652.21342685958</v>
       </c>
       <c r="K42" s="7">
         <f t="shared" si="15"/>
-        <v>223593.69558739039</v>
+        <v>230461.76132215664</v>
       </c>
       <c r="L42" s="7">
         <f t="shared" si="15"/>
-        <v>254558.02606631097</v>
+        <v>262377.21458029316</v>
       </c>
       <c r="M42" s="7">
         <f t="shared" si="15"/>
-        <v>283826.61521046172</v>
+        <v>292544.83888586838</v>
       </c>
       <c r="N42" s="7">
         <f t="shared" si="15"/>
-        <v>315495.2455802242</v>
+        <v>325186.22581988981</v>
       </c>
     </row>
     <row r="43" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2386,11 +2387,11 @@
       </c>
       <c r="K43" s="10">
         <f t="shared" si="16"/>
-        <v>0.78999999999999992</v>
+        <v>0.79</v>
       </c>
       <c r="L43" s="10">
         <f t="shared" si="16"/>
-        <v>0.77500000000000002</v>
+        <v>0.77499999999999991</v>
       </c>
       <c r="M43" s="10">
         <f t="shared" si="16"/>
@@ -2398,7 +2399,7 @@
       </c>
       <c r="N43" s="10">
         <f t="shared" si="16"/>
-        <v>0.74999999999999989</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="45" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2423,23 +2424,23 @@
       </c>
       <c r="J45" s="7">
         <f>J36*0.14</f>
-        <v>33813.371351298003</v>
+        <v>34852.007331371999</v>
       </c>
       <c r="K45" s="7">
         <f>K36*0.13</f>
-        <v>36793.899273874369</v>
+        <v>37924.087306177673</v>
       </c>
       <c r="L45" s="7">
         <f>L36*0.12</f>
-        <v>39415.436294138475</v>
+        <v>40626.149354367975</v>
       </c>
       <c r="M45" s="7">
         <f>M36*0.115</f>
-        <v>43174.683530691931</v>
+        <v>44500.868349040822</v>
       </c>
       <c r="N45" s="7">
         <f>N36*0.11</f>
-        <v>46272.636018432888</v>
+        <v>47693.979786917174</v>
       </c>
     </row>
     <row r="46" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2476,15 +2477,13 @@
       </c>
       <c r="L46" s="10">
         <f t="shared" si="17"/>
-        <v>0.12000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="M46" s="10">
-        <f t="shared" si="17"/>
-        <v>0.115</v>
+        <v>0.12</v>
       </c>
       <c r="N46" s="10">
-        <f t="shared" si="17"/>
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="48" spans="2:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2508,23 +2507,23 @@
       </c>
       <c r="J48" s="7">
         <f>J36*0.301</f>
-        <v>72698.748405290695</v>
+        <v>74931.815762449784</v>
       </c>
       <c r="K48" s="7">
         <f>K36*0.302</f>
-        <v>85475.05831315431</v>
+        <v>88100.572049735827</v>
       </c>
       <c r="L48" s="7">
         <f>L36*0.315</f>
-        <v>103465.5202721135</v>
+        <v>106643.64205521594</v>
       </c>
       <c r="M48" s="7">
         <f>M36*0.3</f>
-        <v>112629.60921050068</v>
+        <v>116089.22178010648</v>
       </c>
       <c r="N48" s="7">
         <f>N36*0.3</f>
-        <v>126198.09823208969</v>
+        <v>130074.49032795592</v>
       </c>
       <c r="P48" s="7"/>
     </row>
@@ -2595,20 +2594,24 @@
         <v>83277</v>
       </c>
       <c r="J51" s="7">
-        <v>86385.2</v>
+        <f>J42-J45-J48</f>
+        <v>89868.390333037794</v>
       </c>
       <c r="K51" s="7">
-        <v>98057</v>
+        <f t="shared" ref="K51:N51" si="19">K42-K45-K48</f>
+        <v>104437.10196624314</v>
       </c>
       <c r="L51" s="7">
-        <v>107730</v>
+        <f t="shared" si="19"/>
+        <v>115107.42317070924</v>
       </c>
       <c r="M51" s="7">
-        <v>127075</v>
+        <f t="shared" si="19"/>
+        <v>131954.74875672106</v>
       </c>
       <c r="N51" s="7">
-        <f>N36*0.37</f>
-        <v>155644.32115291062</v>
+        <f t="shared" si="19"/>
+        <v>147417.75570501672</v>
       </c>
     </row>
     <row r="52" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2620,40 +2623,40 @@
         <v>0.39645040660058173</v>
       </c>
       <c r="F52" s="10">
-        <f t="shared" ref="F52:N52" si="19">F51/F36</f>
+        <f t="shared" ref="F52:N52" si="20">F51/F36</f>
         <v>0.24822269293107735</v>
       </c>
       <c r="G52" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.34655527716416362</v>
       </c>
       <c r="H52" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.42176643303080225</v>
       </c>
       <c r="I52" s="10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.41438352756187613</v>
       </c>
       <c r="J52" s="10">
-        <f t="shared" si="19"/>
-        <v>0.35766702687975976</v>
+        <f t="shared" si="20"/>
+        <v>0.36100000000000004</v>
       </c>
       <c r="K52" s="10">
-        <f t="shared" si="19"/>
-        <v>0.34645444629597438</v>
+        <f t="shared" si="20"/>
+        <v>0.35800000000000004</v>
       </c>
       <c r="L52" s="10">
-        <f t="shared" si="19"/>
-        <v>0.32798317652829034</v>
+        <f t="shared" si="20"/>
+        <v>0.33999999999999991</v>
       </c>
       <c r="M52" s="10">
-        <f t="shared" si="19"/>
-        <v>0.33847671378092437</v>
+        <f t="shared" si="20"/>
+        <v>0.34100000000000003</v>
       </c>
       <c r="N52" s="10">
-        <f t="shared" si="19"/>
-        <v>0.37</v>
+        <f t="shared" si="20"/>
+        <v>0.34</v>
       </c>
     </row>
     <row r="54" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2677,23 +2680,23 @@
       </c>
       <c r="J54" s="7">
         <f>J51*0.14</f>
-        <v>12093.928</v>
+        <v>12581.574646625293</v>
       </c>
       <c r="K54" s="7">
         <f>K51*0.145</f>
-        <v>14218.264999999999</v>
+        <v>15143.379785105253</v>
       </c>
       <c r="L54" s="7">
         <f>L51*0.15</f>
-        <v>16159.5</v>
+        <v>17266.113475606384</v>
       </c>
       <c r="M54" s="7">
         <f>M51*0.17</f>
-        <v>21602.75</v>
+        <v>22432.307288642583</v>
       </c>
       <c r="N54" s="7">
         <f>N51*0.175</f>
-        <v>27237.756201759355</v>
+        <v>25798.107248377924</v>
       </c>
     </row>
     <row r="55" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2705,39 +2708,39 @@
         <v>0.1692511710478472</v>
       </c>
       <c r="F55" s="10">
-        <f t="shared" ref="F55:N55" si="20">F54/F51</f>
+        <f t="shared" ref="F55:N55" si="21">F54/F51</f>
         <v>0.19416134047331146</v>
       </c>
       <c r="G55" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.17819939680434643</v>
       </c>
       <c r="H55" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.11968694599386</v>
       </c>
       <c r="I55" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.30986947176291174</v>
       </c>
       <c r="J55" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.14000000000000001</v>
       </c>
       <c r="K55" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.14499999999999999</v>
       </c>
       <c r="L55" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.15</v>
       </c>
       <c r="M55" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.17</v>
       </c>
       <c r="N55" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.17499999999999999</v>
       </c>
     </row>
@@ -2848,39 +2851,39 @@
         <v>0.42904077126083912</v>
       </c>
       <c r="F60" s="10">
-        <f t="shared" ref="F60:M60" si="21">F59/F63</f>
+        <f t="shared" ref="F60:M60" si="22">F59/F63</f>
         <v>0.27635137284846173</v>
       </c>
       <c r="G60" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.4099244480305142</v>
       </c>
       <c r="H60" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.41598668670818123</v>
       </c>
       <c r="I60" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.2578134736550578</v>
       </c>
       <c r="J60" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.23699999999999999</v>
       </c>
       <c r="K60" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.315</v>
       </c>
       <c r="L60" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.36</v>
       </c>
       <c r="M60" s="10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.41</v>
       </c>
       <c r="N60" s="10">
-        <f t="shared" ref="N60" si="22">N59/N63</f>
+        <f t="shared" ref="N60" si="23">N59/N63</f>
         <v>0.47999999999999993</v>
       </c>
     </row>
@@ -2893,40 +2896,40 @@
         <v>6.7549118537425054E-2</v>
       </c>
       <c r="F61" s="10">
-        <f t="shared" ref="F61:N61" si="23">F59/F36</f>
+        <f t="shared" ref="F61:N61" si="24">F59/F36</f>
         <v>7.44882470478265E-2</v>
       </c>
       <c r="G61" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>8.2852737542808849E-2</v>
       </c>
       <c r="H61" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>9.4212193238946876E-2</v>
       </c>
       <c r="I61" s="10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>9.2642536548470891E-2</v>
       </c>
       <c r="J61" s="10">
-        <f t="shared" si="23"/>
-        <v>0.12265857660007598</v>
+        <f t="shared" si="24"/>
+        <v>0.11900318855570285</v>
       </c>
       <c r="K61" s="10">
-        <f t="shared" si="23"/>
-        <v>0.15303148378182477</v>
+        <f t="shared" si="24"/>
+        <v>0.14847094287441942</v>
       </c>
       <c r="L61" s="10">
-        <f t="shared" si="23"/>
-        <v>0.16125154501829478</v>
+        <f t="shared" si="24"/>
+        <v>0.15644603539854429</v>
       </c>
       <c r="M61" s="10">
-        <f t="shared" si="23"/>
-        <v>0.17031185346784997</v>
+        <f t="shared" si="24"/>
+        <v>0.16523633465589421</v>
       </c>
       <c r="N61" s="10">
-        <f t="shared" si="23"/>
-        <v>0.17439261849671672</v>
+        <f t="shared" si="24"/>
+        <v>0.1691954874819139</v>
       </c>
     </row>
     <row r="63" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3036,40 +3039,40 @@
         <v>5.9357749154152076E-3</v>
       </c>
       <c r="F67" s="10">
-        <f t="shared" ref="F67:N67" si="24">F66/F36</f>
+        <f t="shared" ref="F67:N67" si="25">F66/F36</f>
         <v>4.8709790839472085E-2</v>
       </c>
       <c r="G67" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>2.8465108004329068E-2</v>
       </c>
       <c r="H67" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>6.3829399213378643E-3</v>
       </c>
       <c r="I67" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-4.4286098145955039E-3</v>
       </c>
       <c r="J67" s="10">
-        <f t="shared" si="24"/>
-        <v>-1.8424663826846857E-3</v>
+        <f t="shared" si="25"/>
+        <v>-1.7875584441278574E-3</v>
       </c>
       <c r="K67" s="10">
-        <f t="shared" si="24"/>
-        <v>-5.1884960215552015E-4</v>
+        <f t="shared" si="25"/>
+        <v>-5.0338719679326961E-4</v>
       </c>
       <c r="L67" s="10">
-        <f t="shared" si="24"/>
-        <v>4.4708372294792009E-4</v>
+        <f t="shared" si="25"/>
+        <v>4.337600358402007E-4</v>
       </c>
       <c r="M67" s="10">
-        <f t="shared" si="24"/>
-        <v>9.3875847338145961E-4</v>
+        <f t="shared" si="25"/>
+        <v>9.1078222748598573E-4</v>
       </c>
       <c r="N67" s="10">
-        <f t="shared" si="24"/>
-        <v>1.0472820260487336E-3</v>
+        <f t="shared" si="25"/>
+        <v>1.01607163454397E-3</v>
       </c>
     </row>
     <row r="68" spans="2:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3137,40 +3140,40 @@
         <v>117929</v>
       </c>
       <c r="F71" s="7">
-        <f t="shared" ref="F71:N71" si="25">F36</f>
+        <f t="shared" ref="F71:N71" si="26">F36</f>
         <v>116609</v>
       </c>
       <c r="G71" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>134902</v>
       </c>
       <c r="H71" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>164501</v>
       </c>
       <c r="I71" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>200966</v>
       </c>
       <c r="J71" s="7">
-        <f t="shared" si="25"/>
-        <v>241524.08108069998</v>
+        <f t="shared" si="26"/>
+        <v>248942.90950979997</v>
       </c>
       <c r="K71" s="7">
-        <f t="shared" si="25"/>
-        <v>283029.99441441824</v>
+        <f t="shared" si="26"/>
+        <v>291723.74850905902</v>
       </c>
       <c r="L71" s="7">
-        <f t="shared" si="25"/>
-        <v>328461.96911782061</v>
+        <f t="shared" si="26"/>
+        <v>338551.24461973313</v>
       </c>
       <c r="M71" s="7">
-        <f t="shared" si="25"/>
-        <v>375432.03070166893</v>
+        <f t="shared" si="26"/>
+        <v>386964.07260035496</v>
       </c>
       <c r="N71" s="7">
-        <f t="shared" si="25"/>
-        <v>420660.32744029898</v>
+        <f t="shared" si="26"/>
+        <v>433581.63442651974</v>
       </c>
     </row>
     <row r="72" spans="2:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3184,40 +3187,40 @@
         <v>0.37182574303495608</v>
       </c>
       <c r="F72" s="10">
-        <f t="shared" ref="F72:N72" si="26">F37</f>
+        <f t="shared" ref="F72:N72" si="27">F37</f>
         <v>-1.1193175554782962E-2</v>
       </c>
       <c r="G72" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0.15687468377226457</v>
       </c>
       <c r="H72" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0.21941112807816043</v>
       </c>
       <c r="I72" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0.22167038498246211</v>
       </c>
       <c r="J72" s="10">
-        <f t="shared" si="26"/>
-        <v>0.20181563588218893</v>
+        <f t="shared" si="27"/>
+        <v>0.23873147452703425</v>
       </c>
       <c r="K72" s="10">
-        <f t="shared" si="26"/>
-        <v>0.17184999999999986</v>
+        <f t="shared" si="27"/>
+        <v>0.17184999999999973</v>
       </c>
       <c r="L72" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0.16051999999999986</v>
       </c>
       <c r="M72" s="10">
-        <f t="shared" si="26"/>
-        <v>0.1429999999999999</v>
+        <f t="shared" si="27"/>
+        <v>0.14299999999999999</v>
       </c>
       <c r="N72" s="10">
-        <f t="shared" si="26"/>
-        <v>0.12046999999999997</v>
+        <f t="shared" si="27"/>
+        <v>0.12047000000000004</v>
       </c>
     </row>
     <row r="73" spans="2:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3253,19 +3256,19 @@
         <v>83277</v>
       </c>
       <c r="J74" s="7">
-        <v>86385.2</v>
+        <v>89868.390333037794</v>
       </c>
       <c r="K74" s="7">
-        <v>98057</v>
+        <v>104437.10196624314</v>
       </c>
       <c r="L74" s="7">
-        <v>107730</v>
+        <v>115107.42317070924</v>
       </c>
       <c r="M74" s="7">
-        <v>127075</v>
+        <v>131954.74875672106</v>
       </c>
       <c r="N74" s="7">
-        <v>155644.32115291062</v>
+        <v>147417.75570501672</v>
       </c>
     </row>
     <row r="75" spans="2:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3279,40 +3282,40 @@
         <v>0.39645040660058173</v>
       </c>
       <c r="F75" s="10">
-        <f t="shared" ref="F75:N75" si="27">F74/F71</f>
+        <f t="shared" ref="F75:N75" si="28">F74/F71</f>
         <v>0.24822269293107735</v>
       </c>
       <c r="G75" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.34655527716416362</v>
       </c>
       <c r="H75" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.42176643303080225</v>
       </c>
       <c r="I75" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.41438352756187613</v>
       </c>
       <c r="J75" s="10">
-        <f t="shared" si="27"/>
-        <v>0.35766702687975976</v>
+        <f t="shared" si="28"/>
+        <v>0.36100000000000004</v>
       </c>
       <c r="K75" s="10">
-        <f t="shared" si="27"/>
-        <v>0.34645444629597438</v>
+        <f t="shared" si="28"/>
+        <v>0.35800000000000004</v>
       </c>
       <c r="L75" s="10">
-        <f t="shared" si="27"/>
-        <v>0.32798317652829034</v>
+        <f t="shared" si="28"/>
+        <v>0.33999999999999991</v>
       </c>
       <c r="M75" s="10">
-        <f t="shared" si="27"/>
-        <v>0.33847671378092437</v>
+        <f t="shared" si="28"/>
+        <v>0.34100000000000003</v>
       </c>
       <c r="N75" s="10">
-        <f t="shared" si="27"/>
-        <v>0.37</v>
+        <f t="shared" si="28"/>
+        <v>0.34</v>
       </c>
     </row>
     <row r="76" spans="2:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3327,44 +3330,44 @@
         <v>13</v>
       </c>
       <c r="E77" s="7">
-        <f t="shared" ref="E77:M77" si="28">E54</f>
+        <f t="shared" ref="E77:M77" si="29">E54</f>
         <v>7913</v>
       </c>
       <c r="F77" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>5620</v>
       </c>
       <c r="G77" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>8331</v>
       </c>
       <c r="H77" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>8304</v>
       </c>
       <c r="I77" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>25805</v>
       </c>
       <c r="J77" s="7">
-        <f t="shared" si="28"/>
-        <v>12093.928</v>
+        <f t="shared" si="29"/>
+        <v>12581.574646625293</v>
       </c>
       <c r="K77" s="7">
-        <f t="shared" si="28"/>
-        <v>14218.264999999999</v>
+        <f t="shared" si="29"/>
+        <v>15143.379785105253</v>
       </c>
       <c r="L77" s="7">
-        <f t="shared" si="28"/>
-        <v>16159.5</v>
+        <f t="shared" si="29"/>
+        <v>17266.113475606384</v>
       </c>
       <c r="M77" s="7">
-        <f t="shared" si="28"/>
-        <v>21602.75</v>
+        <f t="shared" si="29"/>
+        <v>22432.307288642583</v>
       </c>
       <c r="N77" s="7">
         <f>N54</f>
-        <v>27237.756201759355</v>
+        <v>25798.107248377924</v>
       </c>
     </row>
     <row r="78" spans="2:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3378,39 +3381,39 @@
         <v>0.1692511710478472</v>
       </c>
       <c r="F78" s="10">
-        <f t="shared" ref="F78:N78" si="29">F55</f>
+        <f t="shared" ref="F78:N78" si="30">F55</f>
         <v>0.19416134047331146</v>
       </c>
       <c r="G78" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.17819939680434643</v>
       </c>
       <c r="H78" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.11968694599386</v>
       </c>
       <c r="I78" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.30986947176291174</v>
       </c>
       <c r="J78" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.14000000000000001</v>
       </c>
       <c r="K78" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.14499999999999999</v>
       </c>
       <c r="L78" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.15</v>
       </c>
       <c r="M78" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.17</v>
       </c>
       <c r="N78" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.17499999999999999</v>
       </c>
     </row>
@@ -3425,40 +3428,40 @@
         <v>38840</v>
       </c>
       <c r="F80" s="29">
-        <f t="shared" ref="F80:N80" si="30">F74-F77</f>
+        <f t="shared" ref="F80:N80" si="31">F74-F77</f>
         <v>23325</v>
       </c>
       <c r="G80" s="29">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>38420</v>
       </c>
       <c r="H80" s="29">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>61077</v>
       </c>
       <c r="I80" s="29">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>57472</v>
       </c>
       <c r="J80" s="29">
-        <f t="shared" si="30"/>
-        <v>74291.271999999997</v>
+        <f t="shared" si="31"/>
+        <v>77286.815686412505</v>
       </c>
       <c r="K80" s="29">
-        <f t="shared" si="30"/>
-        <v>83838.735000000001</v>
+        <f t="shared" si="31"/>
+        <v>89293.722181137884</v>
       </c>
       <c r="L80" s="29">
-        <f t="shared" si="30"/>
-        <v>91570.5</v>
+        <f t="shared" si="31"/>
+        <v>97841.309695102856</v>
       </c>
       <c r="M80" s="29">
-        <f t="shared" si="30"/>
-        <v>105472.25</v>
+        <f t="shared" si="31"/>
+        <v>109522.44146807848</v>
       </c>
       <c r="N80" s="30">
-        <f t="shared" si="30"/>
-        <v>128406.56495115126</v>
+        <f t="shared" si="31"/>
+        <v>121619.6484566388</v>
       </c>
     </row>
     <row r="82" spans="2:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3470,39 +3473,39 @@
         <v>7966</v>
       </c>
       <c r="F82" s="7">
-        <f t="shared" ref="F82:N82" si="31">F59</f>
+        <f t="shared" ref="F82:N82" si="32">F59</f>
         <v>8686</v>
       </c>
       <c r="G82" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>11177</v>
       </c>
       <c r="H82" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>15498</v>
       </c>
       <c r="I82" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>18618</v>
       </c>
       <c r="J82" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>29625</v>
       </c>
       <c r="K82" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>43312.5</v>
       </c>
       <c r="L82" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>52965</v>
       </c>
       <c r="M82" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>63940.524999999994</v>
       </c>
       <c r="N82" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>73360.055999999997</v>
       </c>
       <c r="P82" s="7"/>
@@ -3518,40 +3521,40 @@
         <v>6.7549118537425054E-2</v>
       </c>
       <c r="F83" s="10">
-        <f t="shared" ref="F83:N83" si="32">F82/F71</f>
+        <f t="shared" ref="F83:N83" si="33">F82/F71</f>
         <v>7.44882470478265E-2</v>
       </c>
       <c r="G83" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>8.2852737542808849E-2</v>
       </c>
       <c r="H83" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>9.4212193238946876E-2</v>
       </c>
       <c r="I83" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>9.2642536548470891E-2</v>
       </c>
       <c r="J83" s="10">
-        <f t="shared" si="32"/>
-        <v>0.12265857660007598</v>
+        <f t="shared" si="33"/>
+        <v>0.11900318855570285</v>
       </c>
       <c r="K83" s="10">
-        <f t="shared" si="32"/>
-        <v>0.15303148378182477</v>
+        <f t="shared" si="33"/>
+        <v>0.14847094287441942</v>
       </c>
       <c r="L83" s="10">
-        <f t="shared" si="32"/>
-        <v>0.16125154501829478</v>
+        <f t="shared" si="33"/>
+        <v>0.15644603539854429</v>
       </c>
       <c r="M83" s="10">
-        <f t="shared" si="32"/>
-        <v>0.17031185346784997</v>
+        <f t="shared" si="33"/>
+        <v>0.16523633465589421</v>
       </c>
       <c r="N83" s="10">
-        <f t="shared" si="32"/>
-        <v>0.17439261849671672</v>
+        <f t="shared" si="33"/>
+        <v>0.1691954874819139</v>
       </c>
     </row>
     <row r="85" spans="2:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3563,39 +3566,39 @@
         <v>18567</v>
       </c>
       <c r="F85" s="7">
-        <f t="shared" ref="F85:N85" si="33">F63</f>
+        <f t="shared" ref="F85:N85" si="34">F63</f>
         <v>31431</v>
       </c>
       <c r="G85" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>27266</v>
       </c>
       <c r="H85" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>37256</v>
       </c>
       <c r="I85" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>72215</v>
       </c>
       <c r="J85" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>125000</v>
       </c>
       <c r="K85" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>137500</v>
       </c>
       <c r="L85" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>147125</v>
       </c>
       <c r="M85" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>155952.5</v>
       </c>
       <c r="N85" s="7">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>152833.45000000001</v>
       </c>
       <c r="Q85" s="7"/>
@@ -3611,40 +3614,40 @@
         <v>0.15744218979216307</v>
       </c>
       <c r="F86" s="10">
-        <f t="shared" ref="F86:N86" si="34">F85/F71</f>
+        <f t="shared" ref="F86:N86" si="35">F85/F71</f>
         <v>0.26954180209074774</v>
       </c>
       <c r="G86" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.20211709240782197</v>
       </c>
       <c r="H86" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.22647886638986997</v>
       </c>
       <c r="I86" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.35933939074271271</v>
       </c>
       <c r="J86" s="10">
-        <f t="shared" si="34"/>
-        <v>0.51754673670918139</v>
+        <f t="shared" si="35"/>
+        <v>0.50212315846288125</v>
       </c>
       <c r="K86" s="10">
-        <f t="shared" si="34"/>
-        <v>0.48581423422801517</v>
+        <f t="shared" si="35"/>
+        <v>0.47133632658545849</v>
       </c>
       <c r="L86" s="10">
-        <f t="shared" si="34"/>
-        <v>0.44792095838415219</v>
+        <f t="shared" si="35"/>
+        <v>0.43457232055151196</v>
       </c>
       <c r="M86" s="10">
-        <f t="shared" si="34"/>
-        <v>0.41539476455573171</v>
+        <f t="shared" si="35"/>
+        <v>0.40301545038022979</v>
       </c>
       <c r="N86" s="10">
-        <f t="shared" si="34"/>
-        <v>0.36331795520149324</v>
+        <f t="shared" si="35"/>
+        <v>0.35249059892065404</v>
       </c>
     </row>
     <row r="88" spans="2:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3703,40 +3706,40 @@
         <v>5.9357749154152076E-3</v>
       </c>
       <c r="F89" s="10">
-        <f t="shared" ref="F89:N89" si="35">F88/F71</f>
+        <f t="shared" ref="F89:N89" si="36">F88/F71</f>
         <v>4.8709790839472085E-2</v>
       </c>
       <c r="G89" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>2.8465108004329068E-2</v>
       </c>
       <c r="H89" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>6.3829399213378643E-3</v>
       </c>
       <c r="I89" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>-1.5176696555636277E-2</v>
       </c>
       <c r="J89" s="10">
-        <f t="shared" si="35"/>
-        <v>-6.3140701878520123E-3</v>
+        <f t="shared" si="36"/>
+        <v>-6.1259025332471512E-3</v>
       </c>
       <c r="K89" s="10">
-        <f t="shared" si="35"/>
-        <v>-1.7780800972745355E-3</v>
+        <f t="shared" si="36"/>
+        <v>-1.7250909553027782E-3</v>
       </c>
       <c r="L89" s="10">
-        <f t="shared" si="35"/>
-        <v>1.53214084830467E-3</v>
+        <f t="shared" si="36"/>
+        <v>1.4864810216995642E-3</v>
       </c>
       <c r="M89" s="10">
-        <f t="shared" si="35"/>
-        <v>3.2170936447342155E-3</v>
+        <f t="shared" si="36"/>
+        <v>3.1212199930699511E-3</v>
       </c>
       <c r="N89" s="10">
-        <f t="shared" si="35"/>
-        <v>3.5890002016276826E-3</v>
+        <f t="shared" si="36"/>
+        <v>3.4820432419765267E-3</v>
       </c>
     </row>
     <row r="90" spans="2:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3775,23 +3778,23 @@
       </c>
       <c r="J91" s="12">
         <f>J71*0.11</f>
-        <v>26567.648918876999</v>
+        <v>27383.720046077997</v>
       </c>
       <c r="K91" s="12">
         <f>K71*0.11</f>
-        <v>31133.299385586008</v>
+        <v>32089.612335996491</v>
       </c>
       <c r="L91" s="12">
         <f>L71*0.105</f>
-        <v>34488.506757371164</v>
+        <v>35547.880685071977</v>
       </c>
       <c r="M91" s="12">
-        <f t="shared" ref="M91:N91" si="36">M71*0.105</f>
-        <v>39420.363223675238</v>
+        <f t="shared" ref="M91:N91" si="37">M71*0.105</f>
+        <v>40631.227623037266</v>
       </c>
       <c r="N91" s="12">
-        <f t="shared" si="36"/>
-        <v>44169.334381231391</v>
+        <f t="shared" si="37"/>
+        <v>45526.071614784574</v>
       </c>
     </row>
     <row r="92" spans="2:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3805,40 +3808,40 @@
         <v>7.7673854607433285E-2</v>
       </c>
       <c r="F92" s="10">
-        <f t="shared" ref="F92:J92" si="37">F91/F71</f>
+        <f t="shared" ref="F92:J92" si="38">F91/F71</f>
         <v>0.10283940347657557</v>
       </c>
       <c r="G92" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.10400142325540021</v>
       </c>
       <c r="H92" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>9.2035914675290723E-2</v>
       </c>
       <c r="I92" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>9.9519321676303452E-2</v>
       </c>
       <c r="J92" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.11</v>
       </c>
       <c r="K92" s="10">
-        <f t="shared" ref="K92" si="38">K91/K71</f>
+        <f t="shared" ref="K92" si="39">K91/K71</f>
         <v>0.11</v>
       </c>
       <c r="L92" s="10">
-        <f t="shared" ref="L92" si="39">L91/L71</f>
+        <f t="shared" ref="L92" si="40">L91/L71</f>
         <v>0.105</v>
       </c>
       <c r="M92" s="10">
-        <f t="shared" ref="M92" si="40">M91/M71</f>
-        <v>0.105</v>
+        <f t="shared" ref="M92" si="41">M91/M71</f>
+        <v>0.10499999999999998</v>
       </c>
       <c r="N92" s="10">
-        <f t="shared" ref="N92" si="41">N91/N71</f>
-        <v>0.105</v>
+        <f t="shared" ref="N92" si="42">N91/N71</f>
+        <v>0.10500000000000001</v>
       </c>
     </row>
     <row r="94" spans="2:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3864,24 +3867,24 @@
         <v>20825</v>
       </c>
       <c r="J94" s="7">
-        <f t="shared" ref="J94:N94" si="42">J80+J82-J85+J88+J91</f>
-        <v>3958.9209188769964</v>
+        <f t="shared" ref="J94:N94" si="43">J80+J82-J85+J88+J91</f>
+        <v>7770.5357324905017</v>
       </c>
       <c r="K94" s="7">
-        <f t="shared" si="42"/>
-        <v>20281.284385586008</v>
+        <f t="shared" si="43"/>
+        <v>26692.584517134375</v>
       </c>
       <c r="L94" s="7">
-        <f t="shared" si="42"/>
-        <v>32402.256757371164</v>
+        <f t="shared" si="43"/>
+        <v>39732.440380174834</v>
       </c>
       <c r="M94" s="7">
-        <f t="shared" si="42"/>
-        <v>54088.438223675228</v>
+        <f t="shared" si="43"/>
+        <v>59349.494091115761</v>
       </c>
       <c r="N94" s="7">
-        <f t="shared" si="42"/>
-        <v>94612.255332382629</v>
+        <f t="shared" si="43"/>
+        <v>89182.076071423333</v>
       </c>
       <c r="O94" s="7"/>
       <c r="P94" s="7"/>
@@ -3905,40 +3908,40 @@
         <v>0.33169110227340182</v>
       </c>
       <c r="F95" s="10">
-        <f t="shared" ref="F95:N95" si="43">F94/F71</f>
+        <f t="shared" ref="F95:N95" si="44">F94/F71</f>
         <v>0.15812673121285664</v>
       </c>
       <c r="G95" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.31882403522557118</v>
       </c>
       <c r="H95" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.31673363687758738</v>
       </c>
       <c r="I95" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.10362449369545097</v>
       </c>
       <c r="J95" s="10">
-        <f t="shared" si="43"/>
-        <v>1.6391412819636027E-2</v>
+        <f t="shared" si="44"/>
+        <v>3.1214127559574475E-2</v>
       </c>
       <c r="K95" s="10">
-        <f t="shared" si="43"/>
-        <v>7.1657721039593211E-2</v>
+        <f t="shared" si="44"/>
+        <v>9.1499525333658183E-2</v>
       </c>
       <c r="L95" s="10">
-        <f t="shared" si="43"/>
-        <v>9.8648427531494054E-2</v>
+        <f t="shared" si="44"/>
+        <v>0.11736019586873186</v>
       </c>
       <c r="M95" s="10">
-        <f t="shared" si="43"/>
-        <v>0.1440698549950197</v>
+        <f t="shared" si="44"/>
+        <v>0.15337210426873443</v>
       </c>
       <c r="N95" s="10">
-        <f t="shared" si="43"/>
-        <v>0.22491366349685116</v>
+        <f t="shared" si="44"/>
+        <v>0.20568693180323638</v>
       </c>
     </row>
     <row r="96" spans="2:24" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -3951,23 +3954,23 @@
       <c r="I97" s="7"/>
       <c r="J97" s="7">
         <f>J94/(1+$U$7)^0.5</f>
-        <v>3781.0473805438642</v>
+        <v>7421.4070901648556</v>
       </c>
       <c r="K97" s="7">
         <f>K94/(1+$U$7)^1.5</f>
-        <v>17668.56724127609</v>
+        <v>23253.937739742749</v>
       </c>
       <c r="L97" s="7">
         <f>L94/(1+$U$7)^2.5</f>
-        <v>25748.487541493265</v>
+        <v>31573.425696323538</v>
       </c>
       <c r="M97" s="7">
         <f>M94/(1+$U$7)^3.5</f>
-        <v>39205.90580977514</v>
+        <v>43019.372561132615</v>
       </c>
       <c r="N97" s="7">
         <f>N94/(1+$U$7)^4.5</f>
-        <v>62555.432583284375</v>
+        <v>58965.123785753523</v>
       </c>
       <c r="V97" s="7"/>
     </row>
